--- a/Data/Input_Trips.xlsx
+++ b/Data/Input_Trips.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/912e44f3439e2598/Documents/UiPath/TripPlanner/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrei\Documents\GitHub\Trip-Planner-Bot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{992FDABA-9562-4A30-9E55-54FFDFAF36AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2827F7E-B8C3-4461-8794-ECB3FDC74E69}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B7E4C5-A18E-4516-AD97-B11C57CAABB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1965" yWindow="3360" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>TripId</t>
   </si>
@@ -65,91 +65,22 @@
     <t>Bucuresti</t>
   </si>
   <si>
+    <t>Zbor</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>AccommodationType</t>
+  </si>
+  <si>
+    <t>10.02.2026</t>
+  </si>
+  <si>
+    <t>15.02.2026</t>
+  </si>
+  <si>
     <t>Roma</t>
-  </si>
-  <si>
-    <t>10.06.2025</t>
-  </si>
-  <si>
-    <t>15.06.2025</t>
-  </si>
-  <si>
-    <t>Zbor</t>
-  </si>
-  <si>
-    <t>Hotel</t>
-  </si>
-  <si>
-    <t>Cluj</t>
-  </si>
-  <si>
-    <t>Viena</t>
-  </si>
-  <si>
-    <t>Oricare</t>
-  </si>
-  <si>
-    <t>Apartament</t>
-  </si>
-  <si>
-    <t>Iasi</t>
-  </si>
-  <si>
-    <t>Brasov</t>
-  </si>
-  <si>
-    <t>Tren</t>
-  </si>
-  <si>
-    <t>Timisoara</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>Milano</t>
-  </si>
-  <si>
-    <t>10.04.2024</t>
-  </si>
-  <si>
-    <t>Berlin</t>
-  </si>
-  <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>Fly</t>
-  </si>
-  <si>
-    <t>AccommodationType</t>
-  </si>
-  <si>
-    <t>20.05.2026</t>
-  </si>
-  <si>
-    <t>01.08.2026</t>
-  </si>
-  <si>
-    <t>15.04.2025</t>
-  </si>
-  <si>
-    <t>10.07.2026</t>
-  </si>
-  <si>
-    <t>22.05.2026</t>
-  </si>
-  <si>
-    <t>07.08.2026</t>
-  </si>
-  <si>
-    <t>05.07.2026</t>
-  </si>
-  <si>
-    <t>10.06.2026</t>
-  </si>
-  <si>
-    <t>15.06.2026</t>
   </si>
 </sst>
 </file>
@@ -207,10 +138,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -530,20 +457,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" customWidth="1"/>
-    <col min="9" max="9" width="21.109375" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" customWidth="1"/>
+    <col min="9" max="9" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -569,10 +496,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -580,13 +507,13 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -595,152 +522,10 @@
         <v>2500</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1800</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>800</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>3500</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>2000</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
         <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>-1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
